--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,28; 38,73</t>
+          <t>22,9; 38,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,44; 88,9</t>
+          <t>70,68; 88,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,6; 77,69</t>
+          <t>57,13; 76,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 31,72</t>
+          <t>18,01; 31,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,5; 44,8</t>
+          <t>26,57; 44,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,9; 87,46</t>
+          <t>71,46; 87,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,68; 87,39</t>
+          <t>72,51; 87,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 34,59</t>
+          <t>19,77; 34,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,9; 38,87</t>
+          <t>27,18; 39,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 85,8</t>
+          <t>74,48; 85,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,84; 80,85</t>
+          <t>68,74; 80,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,19; 30,99</t>
+          <t>21,08; 31,26</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 45,39</t>
+          <t>27,56; 45,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,88; 85,19</t>
+          <t>68,95; 86,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,23; 83,89</t>
+          <t>68,04; 83,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,61; 42,36</t>
+          <t>26,34; 43,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,89; 41,82</t>
+          <t>23,49; 41,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,24; 90,59</t>
+          <t>75,36; 90,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,04; 74,61</t>
+          <t>58,5; 74,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,42; 39,35</t>
+          <t>22,48; 38,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,1; 40,3</t>
+          <t>27,84; 41,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75,8; 86,59</t>
+          <t>75,98; 86,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65,21; 76,61</t>
+          <t>65,06; 76,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 37,98</t>
+          <t>26,51; 37,89</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,68; 37,96</t>
+          <t>19,89; 37,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,56; 89,96</t>
+          <t>74,75; 89,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,85; 78,72</t>
+          <t>57,02; 78,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,4; 47,41</t>
+          <t>22,33; 45,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,74; 37,34</t>
+          <t>20,68; 36,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,84; 90,17</t>
+          <t>75,99; 89,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,54; 75,72</t>
+          <t>53,96; 74,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,56; 47,52</t>
+          <t>25,53; 47,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,66; 34,56</t>
+          <t>22,94; 34,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78,06; 88,66</t>
+          <t>77,65; 87,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,42; 74,56</t>
+          <t>59,78; 73,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,88; 42,01</t>
+          <t>26,81; 42,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,98; 35,93</t>
+          <t>23,8; 35,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,49; 87,41</t>
+          <t>76,21; 87,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,53; 75,98</t>
+          <t>63,5; 75,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 34,25</t>
+          <t>18,06; 33,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,35; 37,5</t>
+          <t>25,4; 37,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,15; 91,07</t>
+          <t>82,37; 90,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,25; 75,86</t>
+          <t>63,57; 75,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,91; 36,49</t>
+          <t>24,91; 37,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 34,31</t>
+          <t>26,32; 34,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,06; 87,78</t>
+          <t>81,67; 88,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,41; 74,07</t>
+          <t>65,38; 73,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,84; 33,36</t>
+          <t>21,78; 33,2</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,7; 45,41</t>
+          <t>26,57; 47,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,69; 91,71</t>
+          <t>79,5; 91,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,73; 73,3</t>
+          <t>58,16; 72,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,24; 41,58</t>
+          <t>26,75; 41,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,18; 41,19</t>
+          <t>25,45; 41,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,4; 87,11</t>
+          <t>73,29; 86,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,4; 79,85</t>
+          <t>64,19; 79,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,51; 55,39</t>
+          <t>34,39; 54,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,53; 40,69</t>
+          <t>27,13; 40,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,22; 88,25</t>
+          <t>78,16; 88,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63,26; 74,15</t>
+          <t>63,26; 74,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,26; 47,43</t>
+          <t>33,15; 47,15</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 40,66</t>
+          <t>23,32; 41,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,29; 88,01</t>
+          <t>70,08; 87,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,95; 66,48</t>
+          <t>46,18; 67,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,87; 51,93</t>
+          <t>31,64; 52,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 28,21</t>
+          <t>14,18; 29,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,07; 88,25</t>
+          <t>73,09; 88,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,36; 70,14</t>
+          <t>50,0; 70,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,7; 59,7</t>
+          <t>38,45; 60,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,07; 32,07</t>
+          <t>20,62; 32,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75,07; 86,06</t>
+          <t>74,93; 86,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,26; 65,33</t>
+          <t>50,84; 65,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,8; 52,58</t>
+          <t>38,15; 53,61</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,25; 35,06</t>
+          <t>28,21; 34,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,36</t>
+          <t>79,53; 85,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,24; 71,45</t>
+          <t>64,62; 71,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,05; 34,25</t>
+          <t>26,1; 34,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,54</t>
+          <t>26,77; 33,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,84; 85,92</t>
+          <t>80,62; 86,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,42; 72,72</t>
+          <t>66,49; 73,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,59; 38,43</t>
+          <t>31,14; 38,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,1</t>
+          <t>28,75; 33,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80,98; 84,98</t>
+          <t>81,18; 84,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66,55; 71,04</t>
+          <t>66,53; 71,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,97; 35,48</t>
+          <t>29,91; 35,54</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24461</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50057</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43739</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25140</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25316</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59067</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62657</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>37102</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>49777</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>109124</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>106395</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>18424; 31305</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43269; 54466</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36625; 49205</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18815; 33331</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19031; 31715</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>52461; 63900</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>56249; 67678</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>26935; 47478</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>41339; 59567</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>100278; 115385</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>97391; 114293</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>50739; 75243</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24562</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>51214</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61296</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32039</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21542</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57725</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60081</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>28590</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>46104</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>108939</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>121376</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>60629</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>18929; 31026</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45076; 56366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54753; 67005</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24780; 40663</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15851; 28242</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>51640; 62034</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>52697; 67324</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21354; 36574</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>37911; 56140</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>101734; 116294</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>110952; 130353</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>50131; 71650</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55606</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33769</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17324</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23948</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56781</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39635</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22687</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>40404</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>112387</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73404</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>40011</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11586; 21888</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49727; 59815</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28066; 38606</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11579; 23599</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17360; 30854</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>51643; 60856</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32542; 44770</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16300; 30038</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>32616; 49503</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>104432; 118276</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>65478; 80692</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>31019; 49406</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>44775</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>112799</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111810</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57253</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46486</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>139727</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>116559</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>65439</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>91261</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>252526</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>228368</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>122691</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>36004; 53428</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>104005; 119281</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101679; 121308</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39155; 73537</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37735; 55612</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>132403; 146143</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>105923; 126145</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>54025; 80356</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>78938; 103892</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>242742; 261726</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>213630; 240819</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>94449; 143962</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24606</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80990</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66117</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40893</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27812</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74274</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71345</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>68491</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>52418</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>155264</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>137462</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>109384</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18364; 32514</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>74290; 85886</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>58708; 73571</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31941; 49862</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>21512; 34992</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67432; 79646</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>63217; 78444</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>55923; 89075</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>41681; 61620</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>144950; 163222</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>126151; 148186</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>93505; 132975</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>23551</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43140</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>34216</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>28489</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14934</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>60755</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>40556</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>35295</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>38485</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>103895</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>74771</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>63784</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>17456; 31293</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37780; 47159</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>27640; 40284</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>21800; 36174</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10268; 21026</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>54117; 65596</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>33912; 47902</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>27685; 43704</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>30361; 47866</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>95875; 110472</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>64915; 83974</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>53759; 75531</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>158412</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>393806</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>350945</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>201137</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>448330</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>390832</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>257604</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>318450</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>842135</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>741777</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>458741</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>141785; 174921</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>379315; 407294</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>332609; 367263</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>171095; 224495</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>141508; 176911</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>432661; 462950</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>372914; 409425</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>232476; 286917</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>296495; 342452</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>822918; 861110</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>715618; 766196</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>419406; 498355</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,9; 38,91</t>
+          <t>23,12; 39,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,68; 88,97</t>
+          <t>72,48; 88,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,13; 76,76</t>
+          <t>57,02; 77,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 31,91</t>
+          <t>17,81; 31,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,57; 44,27</t>
+          <t>26,89; 45,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,46; 87,05</t>
+          <t>72,19; 87,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,51; 87,24</t>
+          <t>72,05; 87,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,77; 34,85</t>
+          <t>19,69; 34,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,18; 39,16</t>
+          <t>26,96; 38,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,48; 85,7</t>
+          <t>75,06; 86,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,74; 80,67</t>
+          <t>68,79; 81,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,08; 31,26</t>
+          <t>20,9; 31,01</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,56; 45,17</t>
+          <t>26,64; 44,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,95; 86,21</t>
+          <t>68,76; 85,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,04; 83,27</t>
+          <t>68,17; 82,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,34; 43,22</t>
+          <t>26,21; 42,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,49; 41,85</t>
+          <t>23,09; 41,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,36; 90,53</t>
+          <t>75,84; 90,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,5; 74,74</t>
+          <t>57,94; 74,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,48; 38,5</t>
+          <t>22,23; 38,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 41,23</t>
+          <t>27,26; 39,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75,98; 86,85</t>
+          <t>75,27; 86,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65,06; 76,43</t>
+          <t>65,46; 76,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,51; 37,89</t>
+          <t>27,03; 38,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,89; 37,58</t>
+          <t>20,24; 37,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,75; 89,92</t>
+          <t>74,36; 90,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,02; 78,43</t>
+          <t>57,36; 78,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,33; 45,5</t>
+          <t>22,75; 45,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,68; 36,76</t>
+          <t>21,31; 37,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,99; 89,54</t>
+          <t>75,33; 89,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,96; 74,23</t>
+          <t>55,52; 76,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,53; 47,04</t>
+          <t>24,56; 46,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,94; 34,82</t>
+          <t>22,64; 34,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77,65; 87,95</t>
+          <t>78,16; 88,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,78; 73,67</t>
+          <t>58,66; 73,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,81; 42,7</t>
+          <t>27,32; 43,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 35,31</t>
+          <t>24,55; 35,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,21; 87,4</t>
+          <t>76,22; 87,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,5; 75,76</t>
+          <t>64,15; 75,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,06; 33,92</t>
+          <t>17,26; 33,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 37,43</t>
+          <t>24,4; 37,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,37; 90,92</t>
+          <t>82,21; 90,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,57; 75,71</t>
+          <t>64,24; 75,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,91; 37,06</t>
+          <t>24,46; 36,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,32; 34,65</t>
+          <t>26,32; 34,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,67; 88,06</t>
+          <t>81,4; 88,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 73,7</t>
+          <t>65,39; 73,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,78; 33,2</t>
+          <t>22,47; 33,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,57; 47,04</t>
+          <t>26,85; 45,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,5; 91,9</t>
+          <t>79,34; 91,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,16; 72,89</t>
+          <t>57,78; 73,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,75; 41,75</t>
+          <t>27,55; 41,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,45; 41,4</t>
+          <t>25,86; 41,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,29; 86,56</t>
+          <t>72,45; 86,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,19; 79,65</t>
+          <t>64,85; 79,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,39; 54,78</t>
+          <t>34,11; 55,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,13; 40,1</t>
+          <t>27,87; 40,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78,16; 88,01</t>
+          <t>78,81; 88,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63,26; 74,31</t>
+          <t>62,9; 74,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,15; 47,15</t>
+          <t>33,06; 46,95</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,32; 41,8</t>
+          <t>22,64; 40,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,08; 87,48</t>
+          <t>69,97; 88,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,18; 67,3</t>
+          <t>46,82; 67,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,64; 52,51</t>
+          <t>31,95; 52,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 29,04</t>
+          <t>14,44; 29,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,09; 88,6</t>
+          <t>74,25; 88,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,0; 70,63</t>
+          <t>50,26; 69,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,45; 60,7</t>
+          <t>38,09; 60,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 32,5</t>
+          <t>20,2; 32,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,93; 86,34</t>
+          <t>75,03; 86,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,84; 65,77</t>
+          <t>51,66; 65,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,15; 53,61</t>
+          <t>37,76; 53,31</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,21; 34,8</t>
+          <t>28,07; 34,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,53; 85,39</t>
+          <t>79,67; 85,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,62; 71,35</t>
+          <t>64,7; 71,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,1; 34,24</t>
+          <t>26,05; 34,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,77; 33,47</t>
+          <t>27,52; 34,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,62; 86,26</t>
+          <t>80,97; 86,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,49; 73,0</t>
+          <t>66,36; 72,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,14; 38,43</t>
+          <t>30,99; 38,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,75; 33,21</t>
+          <t>28,6; 33,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81,18; 84,95</t>
+          <t>81,04; 84,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66,53; 71,23</t>
+          <t>66,61; 71,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,91; 35,54</t>
+          <t>29,68; 35,48</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18424; 31305</t>
+          <t>18599; 32047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43269; 54466</t>
+          <t>44373; 54312</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36625; 49205</t>
+          <t>36552; 49363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18815; 33331</t>
+          <t>18600; 32704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19031; 31715</t>
+          <t>19262; 32297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52461; 63900</t>
+          <t>52994; 64231</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56249; 67678</t>
+          <t>55894; 67758</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26935; 47478</t>
+          <t>26828; 47347</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41339; 59567</t>
+          <t>41004; 58898</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100278; 115385</t>
+          <t>101050; 115993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97391; 114293</t>
+          <t>97468; 114881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50739; 75243</t>
+          <t>50297; 74648</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18929; 31026</t>
+          <t>18299; 30753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45076; 56366</t>
+          <t>44952; 56154</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54753; 67005</t>
+          <t>54855; 66562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24780; 40663</t>
+          <t>24659; 39963</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15851; 28242</t>
+          <t>15581; 28178</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51640; 62034</t>
+          <t>51969; 61937</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52697; 67324</t>
+          <t>52192; 67017</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21354; 36574</t>
+          <t>21113; 36771</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37911; 56140</t>
+          <t>37122; 54438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101734; 116294</t>
+          <t>100787; 115579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110952; 130353</t>
+          <t>111637; 130995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50131; 71650</t>
+          <t>51115; 73045</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11586; 21888</t>
+          <t>11787; 22089</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49727; 59815</t>
+          <t>49467; 59950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28066; 38606</t>
+          <t>28237; 38603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11579; 23599</t>
+          <t>11797; 23723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17360; 30854</t>
+          <t>17891; 31522</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51643; 60856</t>
+          <t>51194; 60915</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32542; 44770</t>
+          <t>33488; 46047</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16300; 30038</t>
+          <t>15680; 29850</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32616; 49503</t>
+          <t>32187; 49398</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104432; 118276</t>
+          <t>105115; 118480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65478; 80692</t>
+          <t>64256; 80950</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31019; 49406</t>
+          <t>31617; 49970</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36004; 53428</t>
+          <t>37143; 53470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104005; 119281</t>
+          <t>104027; 119691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101679; 121308</t>
+          <t>102726; 121314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39155; 73537</t>
+          <t>37425; 73707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37735; 55612</t>
+          <t>36253; 56217</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>132403; 146143</t>
+          <t>132138; 146008</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105923; 126145</t>
+          <t>107032; 126285</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54025; 80356</t>
+          <t>53038; 79545</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78938; 103892</t>
+          <t>78911; 103746</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>242742; 261726</t>
+          <t>241919; 261744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213630; 240819</t>
+          <t>213651; 241224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94449; 143962</t>
+          <t>97432; 143117</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18364; 32514</t>
+          <t>18562; 31462</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74290; 85886</t>
+          <t>74147; 85766</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58708; 73571</t>
+          <t>58322; 73988</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31941; 49862</t>
+          <t>32900; 50103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21512; 34992</t>
+          <t>21862; 34798</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67432; 79646</t>
+          <t>66662; 80036</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63217; 78444</t>
+          <t>63871; 78098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55923; 89075</t>
+          <t>55462; 89837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41681; 61620</t>
+          <t>42821; 61786</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144950; 163222</t>
+          <t>146167; 163403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126151; 148186</t>
+          <t>125437; 148667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93505; 132975</t>
+          <t>93253; 132430</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17456; 31293</t>
+          <t>16951; 30272</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37780; 47159</t>
+          <t>37720; 47606</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27640; 40284</t>
+          <t>28026; 40244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21800; 36174</t>
+          <t>22010; 36402</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10268; 21026</t>
+          <t>10452; 21322</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54117; 65596</t>
+          <t>54973; 65676</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33912; 47902</t>
+          <t>34090; 47298</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27685; 43704</t>
+          <t>27423; 43397</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30361; 47866</t>
+          <t>29753; 48241</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95875; 110472</t>
+          <t>95994; 110309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64915; 83974</t>
+          <t>65963; 83457</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53759; 75531</t>
+          <t>53204; 75119</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>141785; 174921</t>
+          <t>141107; 174680</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>379315; 407294</t>
+          <t>380002; 407906</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>332609; 367263</t>
+          <t>332999; 366840</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171095; 224495</t>
+          <t>170764; 223411</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>141508; 176911</t>
+          <t>145465; 180130</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>432661; 462950</t>
+          <t>434523; 461623</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>372914; 409425</t>
+          <t>372225; 407856</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>232476; 286917</t>
+          <t>231341; 284751</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>296495; 342452</t>
+          <t>294891; 342826</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>822918; 861110</t>
+          <t>821446; 861414</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>715618; 766196</t>
+          <t>716448; 765546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>419406; 498355</t>
+          <t>416117; 497487</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80,46%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>30,4%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>81,76%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>68,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,77%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 39,83</t>
+          <t>26,5; 44,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,48; 88,71</t>
+          <t>71,9; 87,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,02; 77,0</t>
+          <t>72,68; 87,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 31,31</t>
+          <t>21,82; 36,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,89; 45,08</t>
+          <t>22,28; 38,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,19; 87,5</t>
+          <t>72,44; 88,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,05; 87,34</t>
+          <t>58,6; 77,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,69; 34,75</t>
+          <t>18,39; 32,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 38,73</t>
+          <t>26,9; 38,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,06; 86,16</t>
+          <t>75,63; 85,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,79; 81,08</t>
+          <t>68,84; 80,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 31,01</t>
+          <t>22,43; 32,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>35,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>78,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>76,17%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>84,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 44,77</t>
+          <t>23,89; 41,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,76; 85,89</t>
+          <t>76,24; 90,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,17; 82,72</t>
+          <t>58,04; 74,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,21; 42,47</t>
+          <t>23,07; 40,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 41,75</t>
+          <t>26,14; 45,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,84; 90,38</t>
+          <t>68,88; 85,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,94; 74,4</t>
+          <t>67,23; 83,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,23; 38,71</t>
+          <t>27,14; 43,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,26; 39,98</t>
+          <t>27,1; 40,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75,27; 86,31</t>
+          <t>75,8; 86,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65,46; 76,81</t>
+          <t>65,21; 76,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,63</t>
+          <t>26,9; 38,9</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65,72%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36,35%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>83,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>68,6%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 37,92</t>
+          <t>20,74; 37,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,36; 90,12</t>
+          <t>75,84; 90,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,36; 78,42</t>
+          <t>55,54; 75,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,75; 45,74</t>
+          <t>25,06; 49,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 37,55</t>
+          <t>19,68; 37,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,33; 89,63</t>
+          <t>75,56; 89,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,52; 76,35</t>
+          <t>56,85; 78,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,56; 46,75</t>
+          <t>23,57; 49,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,64; 34,74</t>
+          <t>22,66; 34,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78,16; 88,1</t>
+          <t>78,06; 88,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,66; 73,9</t>
+          <t>60,42; 74,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 43,18</t>
+          <t>27,67; 43,86</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30,49%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>29,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>82,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>69,83%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,55; 35,34</t>
+          <t>25,35; 37,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,22; 87,7</t>
+          <t>82,15; 91,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,15; 75,76</t>
+          <t>63,25; 75,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 33,99</t>
+          <t>24,71; 36,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,4; 37,84</t>
+          <t>23,98; 35,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,21; 90,84</t>
+          <t>76,49; 87,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,24; 75,79</t>
+          <t>63,53; 75,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 36,68</t>
+          <t>23,0; 34,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,32; 34,6</t>
+          <t>25,81; 34,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,4; 88,07</t>
+          <t>81,06; 87,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,39; 73,83</t>
+          <t>65,41; 74,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,47; 33,0</t>
+          <t>25,74; 34,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42,66%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>86,67%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>65,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,85; 45,52</t>
+          <t>25,18; 41,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,34; 91,78</t>
+          <t>73,4; 87,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,78; 73,3</t>
+          <t>64,4; 79,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,55; 41,95</t>
+          <t>34,24; 54,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 41,17</t>
+          <t>26,7; 45,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 86,99</t>
+          <t>79,69; 91,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,85; 79,3</t>
+          <t>57,73; 73,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,11; 55,24</t>
+          <t>29,02; 43,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,87; 40,21</t>
+          <t>28,53; 40,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78,81; 88,11</t>
+          <t>79,22; 88,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,9; 74,55</t>
+          <t>63,26; 74,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,06; 46,95</t>
+          <t>34,18; 47,15</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>31,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>80,02%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>57,16%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,79%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,64; 40,43</t>
+          <t>13,15; 28,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,97; 88,3</t>
+          <t>74,07; 88,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,82; 67,23</t>
+          <t>49,36; 70,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,95; 52,84</t>
+          <t>40,84; 62,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,44; 29,45</t>
+          <t>23,4; 40,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,25; 88,71</t>
+          <t>69,29; 88,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,26; 69,74</t>
+          <t>46,95; 66,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,09; 60,27</t>
+          <t>29,55; 50,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 32,76</t>
+          <t>21,07; 32,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75,03; 86,21</t>
+          <t>75,07; 86,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,66; 65,36</t>
+          <t>51,26; 65,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,76; 53,31</t>
+          <t>38,04; 52,77</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>69,68%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>31,51%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>68,18%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30,68%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>83,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 34,75</t>
+          <t>27,03; 33,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,52</t>
+          <t>80,84; 85,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,7; 71,27</t>
+          <t>66,42; 72,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,05; 34,08</t>
+          <t>32,58; 39,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,08</t>
+          <t>28,25; 35,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,97; 86,01</t>
+          <t>79,61; 85,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,36; 72,72</t>
+          <t>64,24; 71,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,99; 38,14</t>
+          <t>28,92; 35,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 33,24</t>
+          <t>28,41; 33,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81,04; 84,98</t>
+          <t>80,98; 84,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66,61; 71,17</t>
+          <t>66,55; 71,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,68; 35,48</t>
+          <t>31,54; 36,37</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25316</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59067</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35777</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>24461</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>50057</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>43739</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25140</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59067</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62657</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62241</t>
+          <t>60959</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18599; 32047</t>
+          <t>18984; 32092</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44373; 54312</t>
+          <t>52784; 64202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36552; 49363</t>
+          <t>56382; 67790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18600; 32704</t>
+          <t>26633; 44477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19262; 32297</t>
+          <t>17927; 31162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52994; 64231</t>
+          <t>44348; 54428</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55894; 67758</t>
+          <t>37565; 49803</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26828; 47347</t>
+          <t>18924; 33089</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41004; 58898</t>
+          <t>40908; 59112</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101050; 115993</t>
+          <t>101824; 115510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97468; 114881</t>
+          <t>97534; 114555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50297; 74648</t>
+          <t>50470; 72977</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21542</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57725</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60081</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28025</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24562</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>51214</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>61296</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32039</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21542</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57725</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60081</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>61386</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18299; 30753</t>
+          <t>16123; 28219</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44952; 56154</t>
+          <t>52246; 62077</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54855; 66562</t>
+          <t>52281; 67200</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24659; 39963</t>
+          <t>20945; 36661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15581; 28178</t>
+          <t>17954; 31180</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51969; 61937</t>
+          <t>45035; 55698</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52192; 67017</t>
+          <t>54097; 67509</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21113; 36771</t>
+          <t>26038; 41990</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37122; 54438</t>
+          <t>36906; 54871</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100787; 115579</t>
+          <t>101502; 115942</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111637; 130995</t>
+          <t>111207; 130648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51115; 73045</t>
+          <t>50225; 72641</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23948</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56781</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39635</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20699</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>16457</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>55606</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>33769</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17324</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23948</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56781</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39635</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>39262</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11787; 22089</t>
+          <t>17410; 31343</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49467; 59950</t>
+          <t>51546; 61284</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28237; 38603</t>
+          <t>33499; 45667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11797; 23723</t>
+          <t>14269; 28002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17891; 31522</t>
+          <t>11460; 22112</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51194; 60915</t>
+          <t>50267; 59844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33488; 46047</t>
+          <t>27982; 38749</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15680; 29850</t>
+          <t>12605; 26658</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32187; 49398</t>
+          <t>32218; 49144</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105115; 118480</t>
+          <t>104979; 119233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64256; 80950</t>
+          <t>66186; 81672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31617; 49970</t>
+          <t>30557; 48432</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>172</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46486</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139727</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116559</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>61196</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>44775</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>112799</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>111810</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>57253</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46486</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>139727</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>116559</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65439</t>
+          <t>50543</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>122691</t>
+          <t>111739</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37143; 53470</t>
+          <t>37660; 55712</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104027; 119691</t>
+          <t>132046; 146382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102726; 121314</t>
+          <t>105391; 126404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37425; 73707</t>
+          <t>49595; 73200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36253; 56217</t>
+          <t>36277; 54361</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>132138; 146008</t>
+          <t>104397; 119296</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107032; 126285</t>
+          <t>101730; 121668</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53038; 79545</t>
+          <t>40960; 61961</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78911; 103746</t>
+          <t>77380; 102884</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>241919; 261744</t>
+          <t>240919; 260899</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213651; 241224</t>
+          <t>213723; 242020</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>97432; 143117</t>
+          <t>97487; 129232</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27812</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>74274</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>71345</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63242</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>24606</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>80990</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>66117</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>40893</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>27812</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>74274</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71345</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>109384</t>
+          <t>105823</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18562; 31462</t>
+          <t>21287; 34821</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74147; 85766</t>
+          <t>67529; 80149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58322; 73988</t>
+          <t>63423; 78639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32900; 50103</t>
+          <t>50761; 81174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21862; 34798</t>
+          <t>18457; 31388</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66662; 80036</t>
+          <t>74467; 85706</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63871; 78098</t>
+          <t>58266; 73986</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55462; 89837</t>
+          <t>34457; 51161</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42821; 61786</t>
+          <t>43844; 62521</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146167; 163403</t>
+          <t>146928; 163666</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125437; 148667</t>
+          <t>126143; 147863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93253; 132430</t>
+          <t>91240; 125885</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14934</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60755</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40556</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35236</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23551</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>43140</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>34216</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28489</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14934</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>60755</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>40556</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63784</t>
+          <t>63253</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16951; 30272</t>
+          <t>9523; 20420</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37720; 47606</t>
+          <t>54843; 65341</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28026; 40244</t>
+          <t>33480; 47575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22010; 36402</t>
+          <t>27890; 42649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10452; 21322</t>
+          <t>17518; 30442</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54973; 65676</t>
+          <t>37355; 47448</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34090; 47298</t>
+          <t>28105; 39790</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27423; 43397</t>
+          <t>20791; 35819</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29753; 48241</t>
+          <t>31034; 47229</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95994; 110309</t>
+          <t>96054; 110110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65963; 83457</t>
+          <t>65446; 83410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53204; 75119</t>
+          <t>52747; 73157</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>300</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>448330</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>390832</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>244175</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>158412</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>201137</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>448330</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>390832</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>257604</t>
+          <t>198247</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>458741</t>
+          <t>442422</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>141107; 174680</t>
+          <t>142875; 177263</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>380002; 407906</t>
+          <t>433858; 461115</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>332999; 366840</t>
+          <t>372523; 407872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170764; 223411</t>
+          <t>223829; 271176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>145465; 180130</t>
+          <t>141992; 176220</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>434523; 461623</t>
+          <t>379722; 407139</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>372225; 407856</t>
+          <t>330665; 367766</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>231341; 284751</t>
+          <t>179174; 219893</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>294891; 342826</t>
+          <t>293017; 341379</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>821446; 861414</t>
+          <t>820879; 861409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>716448; 765546</t>
+          <t>715857; 764136</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>416117; 497487</t>
+          <t>412059; 475177</t>
         </is>
       </c>
     </row>
